--- a/AAII_Financials/Yearly/SBRA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SBRA_YR_FIN.xlsx
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>8700</v>
+        <v>-8500</v>
       </c>
       <c r="E14" s="3">
         <v>14000</v>
@@ -1353,7 +1353,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>95300</v>
+        <v>112500</v>
       </c>
       <c r="E22" s="3">
         <v>114800</v>
